--- a/data/trans_bre/P57_AC_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,98</t>
+          <t>-3,31; 6,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 13,62</t>
+          <t>3,39; 13,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,32</t>
+          <t>0,04; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 8,68</t>
+          <t>-1,5; 9,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 8,24</t>
+          <t>-4,33; 8,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 23,02</t>
+          <t>5,18; 23,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 12,39</t>
+          <t>0,07; 11,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 15,7</t>
+          <t>-2,29; 18,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,36</t>
+          <t>0,86; 9,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,52</t>
+          <t>2,88; 11,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,94</t>
+          <t>3,05; 10,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 38,58</t>
+          <t>0,89; 39,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 14,43</t>
+          <t>1,24; 14,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 18,27</t>
+          <t>4,27; 17,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 13,32</t>
+          <t>3,95; 13,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 136,67</t>
+          <t>1,45; 147,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 8,75</t>
+          <t>-1,69; 8,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 9,48</t>
+          <t>-0,16; 9,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,8</t>
+          <t>-3,36; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 3,05</t>
+          <t>-12,27; 3,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 14,71</t>
+          <t>-2,59; 14,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 15,46</t>
+          <t>-0,22; 15,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 4,62</t>
+          <t>-4,0; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 4,72</t>
+          <t>-18,7; 5,23</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,91</t>
+          <t>-2,95; 5,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,56</t>
+          <t>2,95; 10,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,09</t>
+          <t>-3,62; 4,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 3,3</t>
+          <t>-12,87; 3,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,41</t>
+          <t>-4,24; 8,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 15,06</t>
+          <t>3,96; 14,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,38</t>
+          <t>-4,49; 5,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 5,7</t>
+          <t>-21,57; 6,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,21</t>
+          <t>0,45; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,8</t>
+          <t>4,52; 8,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,86</t>
+          <t>1,1; 5,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 16,63</t>
+          <t>-1,63; 19,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,84</t>
+          <t>0,64; 7,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,49</t>
+          <t>6,66; 13,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,21</t>
+          <t>1,37; 6,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 37,78</t>
+          <t>-2,66; 44,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AC_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,15</t>
+          <t>-3,52; 5,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 13,86</t>
+          <t>3,94; 13,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 9,0</t>
+          <t>0,91; 8,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,74</t>
+          <t>-2,37; 8,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,56</t>
+          <t>-4,54; 7,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 23,62</t>
+          <t>6,07; 23,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 11,84</t>
+          <t>1,11; 11,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 18,26</t>
+          <t>-3,75; 14,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,23</t>
+          <t>1,05; 9,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,24</t>
+          <t>2,64; 11,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,14</t>
+          <t>2,98; 9,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 39,24</t>
+          <t>-1,52; 6,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 14,1</t>
+          <t>1,56; 14,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,56</t>
+          <t>3,9; 18,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,64</t>
+          <t>3,85; 13,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 147,35</t>
+          <t>-2,19; 11,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,48%</t>
+          <t>-0,94%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,81</t>
+          <t>-1,99; 9,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,29</t>
+          <t>-0,58; 9,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,11</t>
+          <t>-3,92; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 3,32</t>
+          <t>-5,6; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 14,78</t>
+          <t>-3,08; 15,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 15,32</t>
+          <t>-0,91; 15,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,05</t>
+          <t>-4,59; 5,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 5,23</t>
+          <t>-8,16; 7,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,15%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,55</t>
+          <t>-3,28; 5,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,45</t>
+          <t>2,63; 10,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,32</t>
+          <t>-3,2; 4,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 3,57</t>
+          <t>-3,54; 5,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 8,48</t>
+          <t>-4,69; 7,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,88</t>
+          <t>3,58; 15,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,64</t>
+          <t>-4,0; 5,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 6,17</t>
+          <t>-5,63; 9,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,05</t>
+          <t>0,62; 5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,92</t>
+          <t>4,74; 9,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,1</t>
+          <t>1,26; 4,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 19,23</t>
+          <t>-0,74; 4,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,51</t>
+          <t>0,91; 7,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,62</t>
+          <t>6,96; 13,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,56</t>
+          <t>1,57; 6,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 44,02</t>
+          <t>-1,13; 6,71</t>
         </is>
       </c>
     </row>
